--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-12-2025.xlsx
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>£50.96</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
+          <t>£959.7</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£41.60</t>
+          <t>£42.88</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£41.71</t>
+          <t>£42.88</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
+          <t>£1439.04</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£40.93</t>
+          <t>£42.88</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
+          <t>£1700.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,220.00</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: 'Guide'</t>
+          <t>£1804.16</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
